--- a/data/trans_orig/IP24_R_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8178</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4534</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13259</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,67%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8005</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4059</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13035</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,92%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>12273</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>17097</t>
+          <t>15970</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11651</t>
+          <t>10853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24496</t>
+          <t>23065</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>19,12%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55967</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50886</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>59611</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,25%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>79,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>92,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>65277</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>60247</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>69223</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>89,08%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70274</t>
+          <t>48689</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64347</t>
+          <t>44208</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74573</t>
+          <t>52081</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>135551</t>
+          <t>104656</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128152</t>
+          <t>97561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140997</t>
+          <t>109773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6607</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2934</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13366</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6221</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6509</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6796</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3175</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13891</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16197</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -1176,74 +1176,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>106912</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>100153</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>110585</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>88,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>124114</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>120238</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>126459</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>97774</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>93715</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>100224</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>93,51%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>117853</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>110758</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>121474</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,55%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>88,86%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,45%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>280</t>
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>241967</t>
+          <t>204686</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>234911</t>
+          <t>198187</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>246892</t>
+          <t>209309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>113519</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>113519</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>113519</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>126459</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>126459</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>126459</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>124649</t>
+          <t>100224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>251108</t>
+          <t>213743</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>251108</t>
+          <t>213743</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>251108</t>
+          <t>213743</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7958</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4458</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13253</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>13,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2520</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9892</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5106</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9253</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,03%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8891</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5119</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14123</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8982</t>
+          <t>8371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>19198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -1524,67 +1524,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>53009</t>
+          <t>51419</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48376</t>
+          <t>46124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55748</t>
+          <t>54919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>86,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>51452</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>47305</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>54155</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>90,97%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>95,68%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>58272</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>53040</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>62044</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>86,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>111281</t>
+          <t>102872</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>103888</t>
+          <t>96738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>116449</t>
+          <t>107565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>58268</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>56558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9232</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3982</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18938</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,79%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6044</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9351</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>62930</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>53224</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>68180</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>73,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>68161</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>64099</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>69589</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>68783</t>
+          <t>68699</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59022</t>
+          <t>65076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74510</t>
+          <t>70341</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>136945</t>
+          <t>131627</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126354</t>
+          <t>120133</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>142739</t>
+          <t>137158</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>72162</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>70143</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78134</t>
+          <t>70844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17008</t>
+          <t>20347</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>25218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>20069</t>
+          <t>17921</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15002</t>
+          <t>13482</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25242</t>
+          <t>22472</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>37077</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30293</t>
+          <t>32687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43532</t>
+          <t>45168</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>60,07%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>19232</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>14361</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>24248</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>48,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>61,26%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>17505</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>13595</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>21631</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>50,72%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,39%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>62,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>20650</t>
+          <t>17687</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>13136</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25717</t>
+          <t>22126</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>36919</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31700</t>
+          <t>30019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44939</t>
+          <t>42500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2548,74 +2548,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>45766</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>56186</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>172</t>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>35489</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>26362</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>45856</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>25,33%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>18,82%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>32,74%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>19983</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>13325</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>30950</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>16,2%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>25,09%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47771</t>
+          <t>26178</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>56207</t>
+          <t>53836</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>43882</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71027</t>
+          <t>67016</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>104594</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>94227</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>113721</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>74,67%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>67,26%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>81,18%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>103394</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>92427</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>110052</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>83,8%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>74,91%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>118460</t>
+          <t>103197</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>106913</t>
+          <t>95366</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127817</t>
+          <t>109605</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>221855</t>
+          <t>207791</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>207035</t>
+          <t>194611</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>234180</t>
+          <t>217981</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140083</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140083</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140083</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123377</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123377</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123377</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154684</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>261627</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6508</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2883</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>13025</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>1264</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>5217</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>4879</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,96%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>6367</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>12546</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>7631</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4076</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>14033</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -3234,74 +3234,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>152913</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>146396</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>156538</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>130355</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>126402</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>139250</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>135618</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>140497</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>96,53%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>150428</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>144249</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>153956</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>92,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>98,19%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>389</t>
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>280783</t>
+          <t>292163</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>274700</t>
+          <t>285885</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>284338</t>
+          <t>296005</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159421</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131619</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156795</t>
+          <t>140497</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>299918</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>94319</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>79290</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>113187</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>55847</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>44882</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>72726</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>81121</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>114773</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>131762</t>
+          <t>129735</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>170692</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>602909</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>584041</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>617938</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>86,47%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>83,77%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>88,63%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>850</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>607982</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>591103</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>618947</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>89,04%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>93,24%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>660908</t>
+          <t>572514</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>642924</t>
+          <t>560397</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>676576</t>
+          <t>582782</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1268890</t>
+          <t>1175422</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1247144</t>
+          <t>1154058</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1289764</t>
+          <t>1195015</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,21%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
